--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Explicit Wait (đợi tường minh) linh hoạt và thông minh hơn. Nó sử dụng `ExpectedConditions` (ví dụ: đợi cho đến khi nút bấm hiển thị và có thể click được). Tránh kết hợp cả hai loại wait vì dễ gây ra thời gian chờ không đoán trước được (timeout issues).</v>
       </c>
       <c r="F2" t="str">
+        <v>Implicit Wait bắt buộc phải chạy ban đêm; còn Explicit Wait chỉ chạy ban ngày — giới hạn thời gian chạy</v>
+      </c>
+      <c r="G2" t="str">
         <v>Implicit Wait đợi chung cho tất cả các phần tử; Explicit Wait đợi riêng cho một phần tử cụ thể với một điều kiện xác định (như phần tử có thể click, hiển thị) — đợi chung toàn cục vs đợi điều kiện cụ thể</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Implicit Wait chạy nhanh hơn Explicit Wait gấp 10 lần trong mọi điều kiện — so sánh hiệu năng tốc độ</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Implicit Wait viết bằng mã nguồn Java; còn Explicit Wait viết bằng ngôn ngữ Python — ngôn ngữ lập trình viết</v>
       </c>
-      <c r="I2" t="str">
-        <v>Implicit Wait bắt buộc phải chạy ban đêm; còn Explicit Wait chỉ chạy ban ngày — giới hạn thời gian chạy</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Sử dụng `close()` chỉ tắt tab đang hoạt động. Sử dụng `quit()` ở cuối test suite (thường đặt trong `@AfterSuite` hoặc `@AfterTest`) giúp tắt toàn bộ trình duyệt và tắt tiến trình Webdriver chạy ngầm trên hệ điều hành, tránh rò rỉ tài nguyên (process leaks).</v>
       </c>
       <c r="F3" t="str">
-        <v>close() đóng cửa sổ trình duyệt hiện tại đang active; quit() đóng toàn bộ các cửa sổ đang mở và giải phóng driver session — đóng tab hiện tại vs đóng toàn bộ kết thúc session</v>
+        <v>close() xóa sạch dữ liệu cache; còn quit() lưu lại lịch sử duyệt web của người dùng — dọn dẹp dữ liệu duyệt</v>
       </c>
       <c r="G3" t="str">
-        <v>close() xóa sạch dữ liệu cache; còn quit() lưu lại lịch sử duyệt web của người dùng — dọn dẹp dữ liệu duyệt</v>
+        <v>close() bắt buộc sử dụng cho trình duyệt Chrome; còn quit() chỉ dùng cho Firefox — giới hạn trình duyệt</v>
       </c>
       <c r="H3" t="str">
         <v>close() do dev viết; còn quit() do QA viết tài liệu đặc tả lỗi hệ thống — phân vai trò viết lệnh</v>
       </c>
       <c r="I3" t="str">
-        <v>close() bắt buộc sử dụng cho trình duyệt Chrome; còn quit() chỉ dùng cho Firefox — giới hạn trình duyệt</v>
+        <v>close() đóng cửa sổ trình duyệt hiện tại đang active; quit() đóng toàn bộ các cửa sổ đang mở và giải phóng driver session — đóng tab hiện tại vs đóng toàn bộ kết thúc session</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Khi ID thay đổi động (ví dụ sinh ngẫu nhiên dạng `login-12345`), ta phải tìm kiếm dựa trên các thuộc tính ổn định khác. Hàm `contains(text(), "...")` hoặc `contains(@class, "...")` là giải pháp định vị phần tử bền bỉ.</v>
       </c>
       <c r="F4" t="str">
-        <v>//button[contains(text(), "Đăng nhập")] — sử dụng hàm contains để tìm kiếm chuỗi văn bản chứa bên trong — tìm kiếm chuỗi văn bản mờ</v>
+        <v>//button[@id="login_button"] — sử dụng thuộc tính ID động của nút bấm — sử dụng ID động không ổn định</v>
       </c>
       <c r="G4" t="str">
         <v>/html/body/div[1]/button[1] — sử dụng đường dẫn tuyệt đối bắt buộc — đường dẫn tuyệt đối rủi ro</v>
       </c>
       <c r="H4" t="str">
-        <v>//button[@id="login_button"] — sử dụng thuộc tính ID động của nút bấm — sử dụng ID động không ổn định</v>
+        <v>//button[contains(text(), "Đăng nhập")] — sử dụng hàm contains để tìm kiếm chuỗi văn bản chứa bên trong — tìm kiếm chuỗi văn bản mờ</v>
       </c>
       <c r="I4" t="str">
         <v>//button[@class="btn"] — sử dụng class chung của tất cả các nút trên trang web — sử dụng class chung trùng lặp</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Flaky test là thảm họa của Automation vì nó làm giảm lòng tin vào bộ test. Nguyên nhân số 1 là việc sử dụng `Thread.sleep()` cứng nhắc thay vì sử dụng Explicit Wait để đồng bộ hóa (Synchronization) theo trạng thái render của phần tử.</v>
       </c>
       <c r="F5" t="str">
-        <v>Do bất đồng bộ thời gian tải trang (mạng chậm, phần tử chưa kịp render đã tương tác) hoặc do dữ liệu test không nhất quán giữa các lần chạy — bất đồng bộ thời gian và dữ liệu test</v>
+        <v>Do vi xử lý CPU của máy chủ CI/CD bị quá nóng trong quá trình chạy test — nhiệt độ vi xử lý máy chủ</v>
       </c>
       <c r="G5" t="str">
         <v>Do lập trình viên sửa đổi cấu trúc thuật toán của database liên tục trong ngày — thay đổi cơ sở dữ liệu</v>
       </c>
       <c r="H5" t="str">
-        <v>Do vi xử lý CPU của máy chủ CI/CD bị quá nóng trong quá trình chạy test — nhiệt độ vi xử lý máy chủ</v>
+        <v>Do bất đồng bộ thời gian tải trang (mạng chậm, phần tử chưa kịp render đã tương tác) hoặc do dữ liệu test không nhất quán giữa các lần chạy — bất đồng bộ thời gian và dữ liệu test</v>
       </c>
       <c r="I5" t="str">
         <v>Do kiểm thử viên viết code test bằng tiếng Việt có dấu khiến trình duyệt không đọc hiểu được — tiếng Việt có dấu</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Thiết lập `@BeforeMethod` (chạy trước mỗi test case) giúp đảm bảo môi trường test của mỗi test case hoàn toàn sạch sẽ, độc lập, không bị ảnh hưởng bởi dữ liệu của test case chạy trước đó.</v>
       </c>
       <c r="F6" t="str">
+        <v>Gửi báo cáo lỗi trực tiếp lên văn phòng của khách hàng thông qua đường bưu điện — gửi báo cáo bưu điện</v>
+      </c>
+      <c r="G6" t="str">
         <v>Chạy các bước chuẩn bị (như khởi tạo trình duyệt, xóa cookie, chuẩn bị dữ liệu) trước khi thực thi từng test case cụ thể — chuẩn bị môi trường test</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
+        <v>Xóa bỏ toàn bộ các file ảnh chụp lỗi màn hình cũ đã lưu trong thư mục dự án — dọn dẹp ảnh lỗi</v>
+      </c>
+      <c r="I6" t="str">
         <v>Tự động dịch mã nguồn code test sang ngôn ngữ HTML để hiển thị ra trang web — dịch mã nguồn test</v>
       </c>
-      <c r="H6" t="str">
-        <v>Gửi báo cáo lỗi trực tiếp lên văn phòng của khách hàng thông qua đường bưu điện — gửi báo cáo bưu điện</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Xóa bỏ toàn bộ các file ảnh chụp lỗi màn hình cũ đã lưu trong thư mục dự án — dọn dẹp ảnh lỗi</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Sử dụng lớp Actions để thực hiện chuỗi hành động di chuyển chuột: `Actions action = new Actions(driver); action.moveToElement(element).perform();` — lớp Actions rê chuột</v>
       </c>
       <c r="G7" t="str">
+        <v>Sử dụng câu lệnh `driver.switchTo().frame(element)` để di chuyển trình duyệt — chuyển frame di chuyển</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Yêu cầu lập trình viên Frontend loại bỏ hoàn toàn tính năng rê chuột ra khỏi website — yêu cầu sửa giao diện</v>
+      </c>
+      <c r="I7" t="str">
         <v>Gọi trực tiếp hàm `element.click()` hai lần liên tiếp vào menu cha — click đúp menu cha</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Sử dụng câu lệnh `driver.switchTo().frame(element)` để di chuyển trình duyệt — chuyển frame di chuyển</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Yêu cầu lập trình viên Frontend loại bỏ hoàn toàn tính năng rê chuột ra khỏi website — yêu cầu sửa giao diện</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -658,10 +658,10 @@
         <v>Đo lường thời gian phản hồi trung bình của API khi tải nặng — đo lường hiệu năng phản hồi</v>
       </c>
       <c r="H8" t="str">
+        <v>Xóa bỏ các tài khoản người dùng cũ trong database khi API được gọi thành công — dọn dẹp tài khoản</v>
+      </c>
+      <c r="I8" t="str">
         <v>Mã hóa toàn bộ dữ liệu gửi đi của API bằng thuật toán bảo mật MD5 — mã hóa dữ liệu gửi</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Xóa bỏ các tài khoản người dùng cũ trong database khi API được gọi thành công — dọn dẹp tài khoản</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Mã JavaScript viết trong tab Tests của Postman chạy sau khi nhận được Response. Ví dụ: `pm.test("Status code is 200", function () { pm.response.to.have.status(200); });` giúp tự động hóa khâu xác thực API.</v>
       </c>
       <c r="F9" t="str">
+        <v>Viết tài liệu hướng dẫn sử dụng API bằng ngôn ngữ tiếng Việt có dấu — tài liệu hướng dẫn sử dụng</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Chạy các kịch bản kiểm thử hiệu năng tải trang web bằng cách giả lập click chuột tự động — giả lập click chuột</v>
+      </c>
+      <c r="H9" t="str">
         <v>Viết mã JavaScript để chạy các assertion kiểm tra Response sau khi API gửi request xong (ví dụ kiểm tra Status Code 200) — JavaScript assertions kiểm tra phản hồi</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>Viết mã SQL để truy vấn trực tiếp dữ liệu từ máy chủ cơ sở dữ liệu của khách hàng — SQL truy xuất database</v>
       </c>
-      <c r="H9" t="str">
-        <v>Viết tài liệu hướng dẫn sử dụng API bằng ngôn ngữ tiếng Việt có dấu — tài liệu hướng dẫn sử dụng</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Chạy các kịch bản kiểm thử hiệu năng tải trang web bằng cách giả lập click chuột tự động — giả lập click chuột</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Selenium driver chỉ nhìn thấy tài liệu HTML ở cấp cao nhất (Default Content). Khi phần tử nằm trong thẻ `&lt;iframe&gt;`, ta phải gọi lệnh switch chuyển driver vào trong frame đó. Sau khi thao tác xong, cần gọi `driver.switchTo().defaultContent()` để chuyển driver quay lại trang chính.</v>
       </c>
       <c r="F10" t="str">
+        <v>Vì trình duyệt web đang bị tràn bộ nhớ RAM; cần tắt bớt các tab trình duyệt khác đang mở — tắt bớt tab trình duyệt</v>
+      </c>
+      <c r="G10" t="str">
         <v>Vì phần tử nằm trong một context tài liệu khác; cần gọi câu lệnh `driver.switchTo().frame(iframeElement)` để chuyển ngữ cảnh driver vào trong Iframe trước khi tìm kiếm — chuyển ngữ cảnh driver vào Iframe</v>
       </c>
-      <c r="G10" t="str">
-        <v>Vì trình duyệt web đang bị tràn bộ nhớ RAM; cần tắt bớt các tab trình duyệt khác đang mở — tắt bớt tab trình duyệt</v>
-      </c>
       <c r="H10" t="str">
+        <v>Vì driver của Selenium không hỗ trợ kiểm thử các trang web chứa thẻ Iframe — giới hạn tính năng Selenium</v>
+      </c>
+      <c r="I10" t="str">
         <v>Vì phần tử đó bắt buộc phải hiển thị dạng màu đỏ thì driver mới nhận dạng được — thay đổi màu sắc phần tử</v>
       </c>
-      <c r="I10" t="str">
-        <v>Vì driver của Selenium không hỗ trợ kiểm thử các trang web chứa thẻ Iframe — giới hạn tính năng Selenium</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Sử dụng biến môi trường: `var jsonData = pm.response.json(); pm.environment.set("token", jsonData.token);`. Ở các request sau, điền `Bearer {{token}}` giúp chuỗi test chạy tự động liên mạch hoàn toàn.</v>
       </c>
       <c r="F11" t="str">
+        <v>Copy token thủ công bằng tay và paste vào từng request mỗi khi chạy kiểm thử — copy paste thủ công bất tiện</v>
+      </c>
+      <c r="G11" t="str">
         <v>Trích xuất token từ Response JSON trong tab Tests, lưu vào biến môi trường (Environment Variable) và gọi lại biến này ở phần Authorization Header của các request sau — trích xuất lưu biến môi trường</v>
       </c>
-      <c r="G11" t="str">
-        <v>Copy token thủ công bằng tay và paste vào từng request mỗi khi chạy kiểm thử — copy paste thủ công bất tiện</v>
-      </c>
       <c r="H11" t="str">
+        <v>Tự động tăng giá trị của mã token lên 1 đơn vị sau mỗi lần gửi yêu cầu API thành công — tự tăng giá trị token</v>
+      </c>
+      <c r="I11" t="str">
         <v>Yêu cầu lập trình viên Backend tắt tính năng xác thực bảo mật của API để không cần truyền token — tắt bảo mật API rủi ro</v>
       </c>
-      <c r="I11" t="str">
-        <v>Tự động tăng giá trị của mã token lên 1 đơn vị sau mỗi lần gửi yêu cầu API thành công — tự tăng giá trị token</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
